--- a/data/orders/2026-T4_suivi_ventes.xlsx
+++ b/data/orders/2026-T4_suivi_ventes.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:U10"/>
+  <dimension ref="B1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6.77</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>0</v>
@@ -789,47 +789,119 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="25.5" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>12-oct</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>#1379, #1378</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>524.36</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>13-oct</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>#1382, #1381, #1380</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>14-oct</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>#1384, #1383</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>192.45</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" ht="25.5" customHeight="1">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>oct-26</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>1199.09</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>110.89</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" ht="25.5" customHeight="1">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="D11" s="7" t="n">
+        <v>2095.9</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>193.1</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" ht="25.5" customHeight="1">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>TOTAL PÉRIODE</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>1199.09</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>110.89</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>84</v>
+      <c r="D13" s="7" t="n">
+        <v>2095.9</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>193.1</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B13:C13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/orders/2026-T4_suivi_ventes.xlsx
+++ b/data/orders/2026-T4_suivi_ventes.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:U13"/>
+  <dimension ref="B1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -845,63 +845,231 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>#1384, #1383</t>
+          <t>#1385, #1384, #1383</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>192.45</v>
+        <v>232.45</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>21.59</v>
+        <v>25.58</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>10.83</v>
+        <v>12.83</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="11" ht="25.5" customHeight="1">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>15-oct</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>#1387, #1386</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>16-oct</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>#1391, #1390, #1389, #1388</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>344.68</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>17-oct</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>#1393, #1392</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>18-oct</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>#1395, #1394</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>19-oct</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>#1396</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>20-oct</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>#1398, #1397</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>320.88</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>21-oct</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>#1400, #1399</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="25.5" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>oct-26</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>2095.9</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>193.1</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" ht="25.5" customHeight="1">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="D18" s="7" t="n">
+        <v>3513.81</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>315.09</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>157.97</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" ht="25.5" customHeight="1">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>TOTAL PÉRIODE</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>2095.9</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>193.1</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>108</v>
+      <c r="D20" s="7" t="n">
+        <v>3513.81</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>315.09</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>157.97</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
